--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127078104</v>
       </c>
       <c r="B2" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,3430 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128364539</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78698</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>607806</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7327211</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128364512</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607775</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7326678</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128364521</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608022</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7326748</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128364536</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>607676</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7326923</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128364531</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>608103</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7326855</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128364542</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78009</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608052</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7326905</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128364508</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91277</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>607664</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7326860</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128364522</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608009</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7326713</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128364526</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80163</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>607883</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7326598</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128364533</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91351</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>607928</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7326925</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128364514</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>607776</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7326788</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128364537</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>607897</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7326952</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128364513</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>607761</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7326730</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128364546</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78437</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>607943</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7326659</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128364527</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>607978</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7326964</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128364529</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>607883</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7326598</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128364523</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>607976</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7326679</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128364541</v>
+      </c>
+      <c r="B20" t="n">
+        <v>75147</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>308</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>607675</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7326945</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128364520</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>608065</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7326779</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128364515</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>607656</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7327054</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128364517</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>607902</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7327076</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128364516</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>607722</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7327043</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128364530</v>
+      </c>
+      <c r="B25" t="n">
+        <v>81006</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>607658</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7326856</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128364534</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91369</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>607882</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7326949</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128364545</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78437</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>607771</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7326790</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128364544</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78437</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>607746</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7326692</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128364518</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>608074</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7326859</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128364509</v>
+      </c>
+      <c r="B30" t="n">
+        <v>75155</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>607938</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7326914</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128364535</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91373</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>607955</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7326918</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128364540</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78698</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>353</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>607932</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7326666</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128364538</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78698</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>353</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>607660</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7327032</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128364528</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80038</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>607768</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7327150</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364539</v>
+        <v>128364521</v>
       </c>
       <c r="B3" t="n">
-        <v>78698</v>
+        <v>79650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607806</v>
+        <v>608022</v>
       </c>
       <c r="R3" t="n">
-        <v>7327211</v>
+        <v>7326748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
         <v>128364512</v>
       </c>
       <c r="B4" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364521</v>
+        <v>128364536</v>
       </c>
       <c r="B5" t="n">
-        <v>79649</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608022</v>
+        <v>607676</v>
       </c>
       <c r="R5" t="n">
-        <v>7326748</v>
+        <v>7326923</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364536</v>
+        <v>128364539</v>
       </c>
       <c r="B6" t="n">
-        <v>79031</v>
+        <v>78699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607676</v>
+        <v>607806</v>
       </c>
       <c r="R6" t="n">
-        <v>7326923</v>
+        <v>7327211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128364531</v>
+        <v>128364542</v>
       </c>
       <c r="B7" t="n">
-        <v>78789</v>
+        <v>78010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608103</v>
+        <v>608052</v>
       </c>
       <c r="R7" t="n">
-        <v>7326855</v>
+        <v>7326905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128364542</v>
+        <v>128364531</v>
       </c>
       <c r="B8" t="n">
-        <v>78009</v>
+        <v>78790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608052</v>
+        <v>608103</v>
       </c>
       <c r="R8" t="n">
-        <v>7326905</v>
+        <v>7326855</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,7 +1422,7 @@
         <v>128364508</v>
       </c>
       <c r="B9" t="n">
-        <v>91277</v>
+        <v>91282</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364522</v>
+        <v>128364526</v>
       </c>
       <c r="B10" t="n">
-        <v>79649</v>
+        <v>80164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608009</v>
+        <v>607883</v>
       </c>
       <c r="R10" t="n">
-        <v>7326713</v>
+        <v>7326598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,32 +1633,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364526</v>
+        <v>128364522</v>
       </c>
       <c r="B11" t="n">
-        <v>80163</v>
+        <v>79650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607883</v>
+        <v>608009</v>
       </c>
       <c r="R11" t="n">
-        <v>7326598</v>
+        <v>7326713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128364533</v>
+        <v>128364514</v>
       </c>
       <c r="B12" t="n">
-        <v>91351</v>
+        <v>79650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607928</v>
+        <v>607776</v>
       </c>
       <c r="R12" t="n">
-        <v>7326925</v>
+        <v>7326788</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128364514</v>
+        <v>128364533</v>
       </c>
       <c r="B13" t="n">
-        <v>79649</v>
+        <v>91356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607776</v>
+        <v>607928</v>
       </c>
       <c r="R13" t="n">
-        <v>7326788</v>
+        <v>7326925</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,7 +1957,7 @@
         <v>128364537</v>
       </c>
       <c r="B14" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128364513</v>
+        <v>128364527</v>
       </c>
       <c r="B15" t="n">
-        <v>79649</v>
+        <v>80136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607761</v>
+        <v>607978</v>
       </c>
       <c r="R15" t="n">
-        <v>7326730</v>
+        <v>7326964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,7 +2171,7 @@
         <v>128364546</v>
       </c>
       <c r="B16" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128364527</v>
+        <v>128364513</v>
       </c>
       <c r="B17" t="n">
-        <v>80135</v>
+        <v>79650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607978</v>
+        <v>607761</v>
       </c>
       <c r="R17" t="n">
-        <v>7326964</v>
+        <v>7326730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,32 +2382,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128364529</v>
+        <v>128364523</v>
       </c>
       <c r="B18" t="n">
-        <v>80170</v>
+        <v>79650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607883</v>
+        <v>607976</v>
       </c>
       <c r="R18" t="n">
-        <v>7326598</v>
+        <v>7326679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,32 +2489,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128364523</v>
+        <v>128364529</v>
       </c>
       <c r="B19" t="n">
-        <v>79649</v>
+        <v>80171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607976</v>
+        <v>607883</v>
       </c>
       <c r="R19" t="n">
-        <v>7326679</v>
+        <v>7326598</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2599,7 @@
         <v>128364541</v>
       </c>
       <c r="B20" t="n">
-        <v>75147</v>
+        <v>75148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>128364520</v>
       </c>
       <c r="B21" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128364515</v>
       </c>
       <c r="B22" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128364517</v>
       </c>
       <c r="B23" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128364516</v>
+        <v>128364545</v>
       </c>
       <c r="B24" t="n">
-        <v>79649</v>
+        <v>78438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607722</v>
+        <v>607771</v>
       </c>
       <c r="R24" t="n">
-        <v>7327043</v>
+        <v>7326790</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128364530</v>
+        <v>128364516</v>
       </c>
       <c r="B25" t="n">
-        <v>81006</v>
+        <v>79650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607658</v>
+        <v>607722</v>
       </c>
       <c r="R25" t="n">
-        <v>7326856</v>
+        <v>7327043</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,7 +3241,7 @@
         <v>128364534</v>
       </c>
       <c r="B26" t="n">
-        <v>91369</v>
+        <v>91374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128364545</v>
+        <v>128364530</v>
       </c>
       <c r="B27" t="n">
-        <v>78437</v>
+        <v>81007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607771</v>
+        <v>607658</v>
       </c>
       <c r="R27" t="n">
-        <v>7326790</v>
+        <v>7326856</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3452,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128364544</v>
+        <v>128364518</v>
       </c>
       <c r="B28" t="n">
-        <v>78437</v>
+        <v>79650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607746</v>
+        <v>608074</v>
       </c>
       <c r="R28" t="n">
-        <v>7326692</v>
+        <v>7326859</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128364518</v>
+        <v>128364544</v>
       </c>
       <c r="B29" t="n">
-        <v>79649</v>
+        <v>78438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>608074</v>
+        <v>607746</v>
       </c>
       <c r="R29" t="n">
-        <v>7326859</v>
+        <v>7326692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,7 +3669,7 @@
         <v>128364509</v>
       </c>
       <c r="B30" t="n">
-        <v>75155</v>
+        <v>75156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128364535</v>
+        <v>128364540</v>
       </c>
       <c r="B31" t="n">
-        <v>91373</v>
+        <v>78699</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607955</v>
+        <v>607932</v>
       </c>
       <c r="R31" t="n">
-        <v>7326918</v>
+        <v>7326666</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128364540</v>
+        <v>128364535</v>
       </c>
       <c r="B32" t="n">
-        <v>78698</v>
+        <v>91378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607932</v>
+        <v>607955</v>
       </c>
       <c r="R32" t="n">
-        <v>7326666</v>
+        <v>7326918</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,7 +3990,7 @@
         <v>128364538</v>
       </c>
       <c r="B33" t="n">
-        <v>78698</v>
+        <v>78699</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>128364528</v>
       </c>
       <c r="B34" t="n">
-        <v>80038</v>
+        <v>80039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364521</v>
+        <v>128364539</v>
       </c>
       <c r="B3" t="n">
-        <v>79650</v>
+        <v>78749</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608022</v>
+        <v>607806</v>
       </c>
       <c r="R3" t="n">
-        <v>7326748</v>
+        <v>7327211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364512</v>
+        <v>128364536</v>
       </c>
       <c r="B4" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607775</v>
+        <v>607676</v>
       </c>
       <c r="R4" t="n">
-        <v>7326678</v>
+        <v>7326923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364536</v>
+        <v>128364521</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607676</v>
+        <v>608022</v>
       </c>
       <c r="R5" t="n">
-        <v>7326923</v>
+        <v>7326748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364539</v>
+        <v>128364512</v>
       </c>
       <c r="B6" t="n">
-        <v>78699</v>
+        <v>79702</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607806</v>
+        <v>607775</v>
       </c>
       <c r="R6" t="n">
-        <v>7327211</v>
+        <v>7326678</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128364542</v>
       </c>
       <c r="B7" t="n">
-        <v>78010</v>
+        <v>78055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128364531</v>
       </c>
       <c r="B8" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,32 +1419,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364508</v>
+        <v>128364526</v>
       </c>
       <c r="B9" t="n">
-        <v>91282</v>
+        <v>80217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607664</v>
+        <v>607883</v>
       </c>
       <c r="R9" t="n">
-        <v>7326860</v>
+        <v>7326598</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364526</v>
+        <v>128364522</v>
       </c>
       <c r="B10" t="n">
-        <v>80164</v>
+        <v>79702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607883</v>
+        <v>608009</v>
       </c>
       <c r="R10" t="n">
-        <v>7326598</v>
+        <v>7326713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364522</v>
+        <v>128364508</v>
       </c>
       <c r="B11" t="n">
-        <v>79650</v>
+        <v>91374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608009</v>
+        <v>607664</v>
       </c>
       <c r="R11" t="n">
-        <v>7326713</v>
+        <v>7326860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,7 +1743,7 @@
         <v>128364514</v>
       </c>
       <c r="B12" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128364533</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>128364537</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128364527</v>
       </c>
       <c r="B15" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128364546</v>
       </c>
       <c r="B16" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>128364513</v>
       </c>
       <c r="B17" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>128364523</v>
       </c>
       <c r="B18" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>128364529</v>
       </c>
       <c r="B19" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>128364541</v>
       </c>
       <c r="B20" t="n">
-        <v>75148</v>
+        <v>75163</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>128364520</v>
       </c>
       <c r="B21" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128364515</v>
       </c>
       <c r="B22" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128364517</v>
       </c>
       <c r="B23" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128364545</v>
+        <v>128364534</v>
       </c>
       <c r="B24" t="n">
-        <v>78438</v>
+        <v>91466</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607771</v>
+        <v>607882</v>
       </c>
       <c r="R24" t="n">
-        <v>7326790</v>
+        <v>7326949</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128364516</v>
+        <v>128364530</v>
       </c>
       <c r="B25" t="n">
-        <v>79650</v>
+        <v>81068</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607722</v>
+        <v>607658</v>
       </c>
       <c r="R25" t="n">
-        <v>7327043</v>
+        <v>7326856</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128364534</v>
+        <v>128364545</v>
       </c>
       <c r="B26" t="n">
-        <v>91374</v>
+        <v>78486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,21 +3249,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607882</v>
+        <v>607771</v>
       </c>
       <c r="R26" t="n">
-        <v>7326949</v>
+        <v>7326790</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128364530</v>
+        <v>128364516</v>
       </c>
       <c r="B27" t="n">
-        <v>81007</v>
+        <v>79702</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607658</v>
+        <v>607722</v>
       </c>
       <c r="R27" t="n">
-        <v>7326856</v>
+        <v>7327043</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,7 +3455,7 @@
         <v>128364518</v>
       </c>
       <c r="B28" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>128364544</v>
       </c>
       <c r="B29" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>128364509</v>
       </c>
       <c r="B30" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128364540</v>
       </c>
       <c r="B31" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128364535</v>
       </c>
       <c r="B32" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>128364538</v>
       </c>
       <c r="B33" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>128364528</v>
       </c>
       <c r="B34" t="n">
-        <v>80039</v>
+        <v>80092</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364539</v>
+        <v>128364536</v>
       </c>
       <c r="B3" t="n">
-        <v>78749</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607806</v>
+        <v>607676</v>
       </c>
       <c r="R3" t="n">
-        <v>7327211</v>
+        <v>7326923</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364536</v>
+        <v>128364539</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>78749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607676</v>
+        <v>607806</v>
       </c>
       <c r="R4" t="n">
-        <v>7326923</v>
+        <v>7327211</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364521</v>
+        <v>128364512</v>
       </c>
       <c r="B5" t="n">
         <v>79702</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608022</v>
+        <v>607775</v>
       </c>
       <c r="R5" t="n">
-        <v>7326748</v>
+        <v>7326678</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364512</v>
+        <v>128364521</v>
       </c>
       <c r="B6" t="n">
         <v>79702</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607775</v>
+        <v>608022</v>
       </c>
       <c r="R6" t="n">
-        <v>7326678</v>
+        <v>7326748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128364544</v>
+        <v>128364509</v>
       </c>
       <c r="B29" t="n">
-        <v>78486</v>
+        <v>75171</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607746</v>
+        <v>607938</v>
       </c>
       <c r="R29" t="n">
-        <v>7326692</v>
+        <v>7326914</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128364509</v>
+        <v>128364544</v>
       </c>
       <c r="B30" t="n">
-        <v>75171</v>
+        <v>78486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607938</v>
+        <v>607746</v>
       </c>
       <c r="R30" t="n">
-        <v>7326914</v>
+        <v>7326692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364536</v>
+        <v>128364521</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607676</v>
+        <v>608022</v>
       </c>
       <c r="R3" t="n">
-        <v>7326923</v>
+        <v>7326748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364539</v>
+        <v>128364512</v>
       </c>
       <c r="B4" t="n">
-        <v>78749</v>
+        <v>79702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607806</v>
+        <v>607775</v>
       </c>
       <c r="R4" t="n">
-        <v>7327211</v>
+        <v>7326678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364512</v>
+        <v>128364536</v>
       </c>
       <c r="B5" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607775</v>
+        <v>607676</v>
       </c>
       <c r="R5" t="n">
-        <v>7326678</v>
+        <v>7326923</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364521</v>
+        <v>128364539</v>
       </c>
       <c r="B6" t="n">
-        <v>79702</v>
+        <v>78749</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608022</v>
+        <v>607806</v>
       </c>
       <c r="R6" t="n">
-        <v>7326748</v>
+        <v>7327211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1419,32 +1419,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364526</v>
+        <v>128364508</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>91374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607883</v>
+        <v>607664</v>
       </c>
       <c r="R9" t="n">
-        <v>7326598</v>
+        <v>7326860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364522</v>
+        <v>128364526</v>
       </c>
       <c r="B10" t="n">
-        <v>79702</v>
+        <v>80217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608009</v>
+        <v>607883</v>
       </c>
       <c r="R10" t="n">
-        <v>7326713</v>
+        <v>7326598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364508</v>
+        <v>128364522</v>
       </c>
       <c r="B11" t="n">
-        <v>91374</v>
+        <v>79702</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607664</v>
+        <v>608009</v>
       </c>
       <c r="R11" t="n">
-        <v>7326860</v>
+        <v>7326713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128364514</v>
+        <v>128364533</v>
       </c>
       <c r="B12" t="n">
-        <v>79702</v>
+        <v>91448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607776</v>
+        <v>607928</v>
       </c>
       <c r="R12" t="n">
-        <v>7326788</v>
+        <v>7326925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128364533</v>
+        <v>128364514</v>
       </c>
       <c r="B13" t="n">
-        <v>91448</v>
+        <v>79702</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607928</v>
+        <v>607776</v>
       </c>
       <c r="R13" t="n">
-        <v>7326925</v>
+        <v>7326788</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128364509</v>
+        <v>128364544</v>
       </c>
       <c r="B29" t="n">
-        <v>75171</v>
+        <v>78486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607938</v>
+        <v>607746</v>
       </c>
       <c r="R29" t="n">
-        <v>7326914</v>
+        <v>7326692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128364544</v>
+        <v>128364509</v>
       </c>
       <c r="B30" t="n">
-        <v>78486</v>
+        <v>75171</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607746</v>
+        <v>607938</v>
       </c>
       <c r="R30" t="n">
-        <v>7326692</v>
+        <v>7326914</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128364521</v>
       </c>
       <c r="B3" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128364512</v>
       </c>
       <c r="B4" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128364536</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128364539</v>
       </c>
       <c r="B6" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128364542</v>
       </c>
       <c r="B7" t="n">
-        <v>78055</v>
+        <v>78059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128364531</v>
       </c>
       <c r="B8" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,32 +1419,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364508</v>
+        <v>128364526</v>
       </c>
       <c r="B9" t="n">
-        <v>91374</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607664</v>
+        <v>607883</v>
       </c>
       <c r="R9" t="n">
-        <v>7326860</v>
+        <v>7326598</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364526</v>
+        <v>128364522</v>
       </c>
       <c r="B10" t="n">
-        <v>80217</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607883</v>
+        <v>608009</v>
       </c>
       <c r="R10" t="n">
-        <v>7326598</v>
+        <v>7326713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364522</v>
+        <v>128364508</v>
       </c>
       <c r="B11" t="n">
-        <v>79702</v>
+        <v>91386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608009</v>
+        <v>607664</v>
       </c>
       <c r="R11" t="n">
-        <v>7326713</v>
+        <v>7326860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128364533</v>
+        <v>128364514</v>
       </c>
       <c r="B12" t="n">
-        <v>91448</v>
+        <v>79706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607928</v>
+        <v>607776</v>
       </c>
       <c r="R12" t="n">
-        <v>7326925</v>
+        <v>7326788</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128364514</v>
+        <v>128364533</v>
       </c>
       <c r="B13" t="n">
-        <v>79702</v>
+        <v>91460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607776</v>
+        <v>607928</v>
       </c>
       <c r="R13" t="n">
-        <v>7326788</v>
+        <v>7326925</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,7 +1957,7 @@
         <v>128364537</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128364527</v>
+        <v>128364513</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607978</v>
+        <v>607761</v>
       </c>
       <c r="R15" t="n">
-        <v>7326964</v>
+        <v>7326730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128364546</v>
+        <v>128364523</v>
       </c>
       <c r="B16" t="n">
-        <v>78486</v>
+        <v>79706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607943</v>
+        <v>607976</v>
       </c>
       <c r="R16" t="n">
-        <v>7326659</v>
+        <v>7326679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128364513</v>
+        <v>128364527</v>
       </c>
       <c r="B17" t="n">
-        <v>79702</v>
+        <v>80193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607761</v>
+        <v>607978</v>
       </c>
       <c r="R17" t="n">
-        <v>7326730</v>
+        <v>7326964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128364523</v>
+        <v>128364546</v>
       </c>
       <c r="B18" t="n">
-        <v>79702</v>
+        <v>78490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607976</v>
+        <v>607943</v>
       </c>
       <c r="R18" t="n">
-        <v>7326679</v>
+        <v>7326659</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,7 +2492,7 @@
         <v>128364529</v>
       </c>
       <c r="B19" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>128364541</v>
       </c>
       <c r="B20" t="n">
-        <v>75163</v>
+        <v>75167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>128364520</v>
       </c>
       <c r="B21" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128364515</v>
       </c>
       <c r="B22" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128364517</v>
       </c>
       <c r="B23" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128364534</v>
+        <v>128364545</v>
       </c>
       <c r="B24" t="n">
-        <v>91466</v>
+        <v>78490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607882</v>
+        <v>607771</v>
       </c>
       <c r="R24" t="n">
-        <v>7326949</v>
+        <v>7326790</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128364530</v>
+        <v>128364516</v>
       </c>
       <c r="B25" t="n">
-        <v>81068</v>
+        <v>79706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607658</v>
+        <v>607722</v>
       </c>
       <c r="R25" t="n">
-        <v>7326856</v>
+        <v>7327043</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128364545</v>
+        <v>128364534</v>
       </c>
       <c r="B26" t="n">
-        <v>78486</v>
+        <v>91478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,21 +3249,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607771</v>
+        <v>607882</v>
       </c>
       <c r="R26" t="n">
-        <v>7326790</v>
+        <v>7326949</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128364516</v>
+        <v>128364530</v>
       </c>
       <c r="B27" t="n">
-        <v>79702</v>
+        <v>81072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607722</v>
+        <v>607658</v>
       </c>
       <c r="R27" t="n">
-        <v>7327043</v>
+        <v>7326856</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,7 +3455,7 @@
         <v>128364518</v>
       </c>
       <c r="B28" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>128364544</v>
       </c>
       <c r="B29" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>128364509</v>
       </c>
       <c r="B30" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128364540</v>
       </c>
       <c r="B31" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128364535</v>
       </c>
       <c r="B32" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>128364538</v>
       </c>
       <c r="B33" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>128364528</v>
       </c>
       <c r="B34" t="n">
-        <v>80092</v>
+        <v>80096</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -1419,32 +1419,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364526</v>
+        <v>128364508</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>91386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607883</v>
+        <v>607664</v>
       </c>
       <c r="R9" t="n">
-        <v>7326598</v>
+        <v>7326860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364522</v>
+        <v>128364526</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608009</v>
+        <v>607883</v>
       </c>
       <c r="R10" t="n">
-        <v>7326713</v>
+        <v>7326598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364508</v>
+        <v>128364522</v>
       </c>
       <c r="B11" t="n">
-        <v>91386</v>
+        <v>79706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607664</v>
+        <v>608009</v>
       </c>
       <c r="R11" t="n">
-        <v>7326860</v>
+        <v>7326713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128364514</v>
+        <v>128364533</v>
       </c>
       <c r="B12" t="n">
-        <v>79706</v>
+        <v>91460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607776</v>
+        <v>607928</v>
       </c>
       <c r="R12" t="n">
-        <v>7326788</v>
+        <v>7326925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128364533</v>
+        <v>128364514</v>
       </c>
       <c r="B13" t="n">
-        <v>91460</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607928</v>
+        <v>607776</v>
       </c>
       <c r="R13" t="n">
-        <v>7326925</v>
+        <v>7326788</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128364513</v>
+        <v>128364527</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>80193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607761</v>
+        <v>607978</v>
       </c>
       <c r="R15" t="n">
-        <v>7326730</v>
+        <v>7326964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128364523</v>
+        <v>128364546</v>
       </c>
       <c r="B16" t="n">
-        <v>79706</v>
+        <v>78490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607976</v>
+        <v>607943</v>
       </c>
       <c r="R16" t="n">
-        <v>7326679</v>
+        <v>7326659</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128364527</v>
+        <v>128364513</v>
       </c>
       <c r="B17" t="n">
-        <v>80193</v>
+        <v>79706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607978</v>
+        <v>607761</v>
       </c>
       <c r="R17" t="n">
-        <v>7326964</v>
+        <v>7326730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128364546</v>
+        <v>128364523</v>
       </c>
       <c r="B18" t="n">
-        <v>78490</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607943</v>
+        <v>607976</v>
       </c>
       <c r="R18" t="n">
-        <v>7326659</v>
+        <v>7326679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128364520</v>
+        <v>128364515</v>
       </c>
       <c r="B21" t="n">
         <v>79706</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608065</v>
+        <v>607656</v>
       </c>
       <c r="R21" t="n">
-        <v>7326779</v>
+        <v>7327054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128364515</v>
+        <v>128364520</v>
       </c>
       <c r="B22" t="n">
         <v>79706</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607656</v>
+        <v>608065</v>
       </c>
       <c r="R22" t="n">
-        <v>7327054</v>
+        <v>7326779</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128364540</v>
+        <v>128364535</v>
       </c>
       <c r="B31" t="n">
-        <v>78753</v>
+        <v>91482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607932</v>
+        <v>607955</v>
       </c>
       <c r="R31" t="n">
-        <v>7326666</v>
+        <v>7326918</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128364535</v>
+        <v>128364540</v>
       </c>
       <c r="B32" t="n">
-        <v>91482</v>
+        <v>78753</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607955</v>
+        <v>607932</v>
       </c>
       <c r="R32" t="n">
-        <v>7326918</v>
+        <v>7326666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364521</v>
+        <v>128364539</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>78755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608022</v>
+        <v>607806</v>
       </c>
       <c r="R3" t="n">
-        <v>7326748</v>
+        <v>7327211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364512</v>
+        <v>128364521</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607775</v>
+        <v>608022</v>
       </c>
       <c r="R4" t="n">
-        <v>7326678</v>
+        <v>7326748</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364536</v>
+        <v>128364512</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607676</v>
+        <v>607775</v>
       </c>
       <c r="R5" t="n">
-        <v>7326923</v>
+        <v>7326678</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364539</v>
+        <v>128364536</v>
       </c>
       <c r="B6" t="n">
-        <v>78753</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607806</v>
+        <v>607676</v>
       </c>
       <c r="R6" t="n">
-        <v>7327211</v>
+        <v>7326923</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128364542</v>
       </c>
       <c r="B7" t="n">
-        <v>78059</v>
+        <v>78061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128364531</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>128364508</v>
       </c>
       <c r="B9" t="n">
-        <v>91386</v>
+        <v>91388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128364526</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>128364522</v>
       </c>
       <c r="B11" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>128364533</v>
       </c>
       <c r="B12" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128364514</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>128364537</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>128364527</v>
       </c>
       <c r="B15" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>128364546</v>
       </c>
       <c r="B16" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>128364513</v>
       </c>
       <c r="B17" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>128364523</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>128364529</v>
       </c>
       <c r="B19" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>128364541</v>
       </c>
       <c r="B20" t="n">
-        <v>75167</v>
+        <v>75169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128364515</v>
+        <v>128364520</v>
       </c>
       <c r="B21" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607656</v>
+        <v>608065</v>
       </c>
       <c r="R21" t="n">
-        <v>7327054</v>
+        <v>7326779</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128364520</v>
+        <v>128364515</v>
       </c>
       <c r="B22" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>608065</v>
+        <v>607656</v>
       </c>
       <c r="R22" t="n">
-        <v>7326779</v>
+        <v>7327054</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,7 +2920,7 @@
         <v>128364517</v>
       </c>
       <c r="B23" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>128364545</v>
       </c>
       <c r="B24" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>128364516</v>
       </c>
       <c r="B25" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>128364534</v>
       </c>
       <c r="B26" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128364530</v>
       </c>
       <c r="B27" t="n">
-        <v>81072</v>
+        <v>81074</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>128364518</v>
       </c>
       <c r="B28" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>128364544</v>
       </c>
       <c r="B29" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>128364509</v>
       </c>
       <c r="B30" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128364535</v>
       </c>
       <c r="B31" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128364540</v>
       </c>
       <c r="B32" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>128364538</v>
       </c>
       <c r="B33" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>128364528</v>
       </c>
       <c r="B34" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -1419,32 +1419,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364508</v>
+        <v>128364526</v>
       </c>
       <c r="B9" t="n">
-        <v>91388</v>
+        <v>80223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607664</v>
+        <v>607883</v>
       </c>
       <c r="R9" t="n">
-        <v>7326860</v>
+        <v>7326598</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364526</v>
+        <v>128364522</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>79708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607883</v>
+        <v>608009</v>
       </c>
       <c r="R10" t="n">
-        <v>7326598</v>
+        <v>7326713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364522</v>
+        <v>128364508</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>91388</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608009</v>
+        <v>607664</v>
       </c>
       <c r="R11" t="n">
-        <v>7326713</v>
+        <v>7326860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128364533</v>
+        <v>128364514</v>
       </c>
       <c r="B12" t="n">
-        <v>91462</v>
+        <v>79708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607928</v>
+        <v>607776</v>
       </c>
       <c r="R12" t="n">
-        <v>7326925</v>
+        <v>7326788</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128364514</v>
+        <v>128364533</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>91462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607776</v>
+        <v>607928</v>
       </c>
       <c r="R13" t="n">
-        <v>7326788</v>
+        <v>7326925</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128364545</v>
+        <v>128364534</v>
       </c>
       <c r="B24" t="n">
-        <v>78492</v>
+        <v>91480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607771</v>
+        <v>607882</v>
       </c>
       <c r="R24" t="n">
-        <v>7326790</v>
+        <v>7326949</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128364516</v>
+        <v>128364530</v>
       </c>
       <c r="B25" t="n">
-        <v>79708</v>
+        <v>81074</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607722</v>
+        <v>607658</v>
       </c>
       <c r="R25" t="n">
-        <v>7327043</v>
+        <v>7326856</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128364534</v>
+        <v>128364545</v>
       </c>
       <c r="B26" t="n">
-        <v>91480</v>
+        <v>78492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,21 +3249,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607882</v>
+        <v>607771</v>
       </c>
       <c r="R26" t="n">
-        <v>7326949</v>
+        <v>7326790</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128364530</v>
+        <v>128364516</v>
       </c>
       <c r="B27" t="n">
-        <v>81074</v>
+        <v>79708</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607658</v>
+        <v>607722</v>
       </c>
       <c r="R27" t="n">
-        <v>7326856</v>
+        <v>7327043</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128364535</v>
+        <v>128364540</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>78755</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607955</v>
+        <v>607932</v>
       </c>
       <c r="R31" t="n">
-        <v>7326918</v>
+        <v>7326666</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128364540</v>
+        <v>128364535</v>
       </c>
       <c r="B32" t="n">
-        <v>78755</v>
+        <v>91484</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607932</v>
+        <v>607955</v>
       </c>
       <c r="R32" t="n">
-        <v>7326666</v>
+        <v>7326918</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -1419,32 +1419,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364526</v>
+        <v>128364508</v>
       </c>
       <c r="B9" t="n">
-        <v>80223</v>
+        <v>91388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607883</v>
+        <v>607664</v>
       </c>
       <c r="R9" t="n">
-        <v>7326598</v>
+        <v>7326860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364522</v>
+        <v>128364526</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608009</v>
+        <v>607883</v>
       </c>
       <c r="R10" t="n">
-        <v>7326713</v>
+        <v>7326598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364508</v>
+        <v>128364522</v>
       </c>
       <c r="B11" t="n">
-        <v>91388</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607664</v>
+        <v>608009</v>
       </c>
       <c r="R11" t="n">
-        <v>7326860</v>
+        <v>7326713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128364514</v>
+        <v>128364533</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>91462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607776</v>
+        <v>607928</v>
       </c>
       <c r="R12" t="n">
-        <v>7326788</v>
+        <v>7326925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128364533</v>
+        <v>128364514</v>
       </c>
       <c r="B13" t="n">
-        <v>91462</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607928</v>
+        <v>607776</v>
       </c>
       <c r="R13" t="n">
-        <v>7326925</v>
+        <v>7326788</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364539</v>
+        <v>128364521</v>
       </c>
       <c r="B3" t="n">
-        <v>78755</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607806</v>
+        <v>608022</v>
       </c>
       <c r="R3" t="n">
-        <v>7327211</v>
+        <v>7326748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364521</v>
+        <v>128364512</v>
       </c>
       <c r="B4" t="n">
         <v>79708</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608022</v>
+        <v>607775</v>
       </c>
       <c r="R4" t="n">
-        <v>7326748</v>
+        <v>7326678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364512</v>
+        <v>128364539</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>78755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607775</v>
+        <v>607806</v>
       </c>
       <c r="R5" t="n">
-        <v>7326678</v>
+        <v>7327211</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364508</v>
+        <v>128364522</v>
       </c>
       <c r="B9" t="n">
-        <v>91388</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607664</v>
+        <v>608009</v>
       </c>
       <c r="R9" t="n">
-        <v>7326860</v>
+        <v>7326713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364522</v>
+        <v>128364508</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>91389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608009</v>
+        <v>607664</v>
       </c>
       <c r="R11" t="n">
-        <v>7326713</v>
+        <v>7326860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,7 +1743,7 @@
         <v>128364533</v>
       </c>
       <c r="B12" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128364534</v>
+        <v>128364530</v>
       </c>
       <c r="B24" t="n">
-        <v>91480</v>
+        <v>81074</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607882</v>
+        <v>607658</v>
       </c>
       <c r="R24" t="n">
-        <v>7326949</v>
+        <v>7326856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128364530</v>
+        <v>128364534</v>
       </c>
       <c r="B25" t="n">
-        <v>81074</v>
+        <v>91481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607658</v>
+        <v>607882</v>
       </c>
       <c r="R25" t="n">
-        <v>7326856</v>
+        <v>7326949</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3452,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128364518</v>
+        <v>128364544</v>
       </c>
       <c r="B28" t="n">
-        <v>79708</v>
+        <v>78492</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>608074</v>
+        <v>607746</v>
       </c>
       <c r="R28" t="n">
-        <v>7326859</v>
+        <v>7326692</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128364544</v>
+        <v>128364509</v>
       </c>
       <c r="B29" t="n">
-        <v>78492</v>
+        <v>75177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607746</v>
+        <v>607938</v>
       </c>
       <c r="R29" t="n">
-        <v>7326692</v>
+        <v>7326914</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128364509</v>
+        <v>128364518</v>
       </c>
       <c r="B30" t="n">
-        <v>75177</v>
+        <v>79708</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607938</v>
+        <v>608074</v>
       </c>
       <c r="R30" t="n">
-        <v>7326914</v>
+        <v>7326859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,7 +3883,7 @@
         <v>128364535</v>
       </c>
       <c r="B32" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364521</v>
+        <v>128364539</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>78755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608022</v>
+        <v>607806</v>
       </c>
       <c r="R3" t="n">
-        <v>7326748</v>
+        <v>7327211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364512</v>
+        <v>128364536</v>
       </c>
       <c r="B4" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607775</v>
+        <v>607676</v>
       </c>
       <c r="R4" t="n">
-        <v>7326678</v>
+        <v>7326923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364539</v>
+        <v>128364521</v>
       </c>
       <c r="B5" t="n">
-        <v>78755</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607806</v>
+        <v>608022</v>
       </c>
       <c r="R5" t="n">
-        <v>7327211</v>
+        <v>7326748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364536</v>
+        <v>128364512</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607676</v>
+        <v>607775</v>
       </c>
       <c r="R6" t="n">
-        <v>7326923</v>
+        <v>7326678</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128364527</v>
+        <v>128364513</v>
       </c>
       <c r="B15" t="n">
-        <v>80195</v>
+        <v>79708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607978</v>
+        <v>607761</v>
       </c>
       <c r="R15" t="n">
-        <v>7326964</v>
+        <v>7326730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128364546</v>
+        <v>128364523</v>
       </c>
       <c r="B16" t="n">
-        <v>78492</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607943</v>
+        <v>607976</v>
       </c>
       <c r="R16" t="n">
-        <v>7326659</v>
+        <v>7326679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128364513</v>
+        <v>128364527</v>
       </c>
       <c r="B17" t="n">
-        <v>79708</v>
+        <v>80195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607761</v>
+        <v>607978</v>
       </c>
       <c r="R17" t="n">
-        <v>7326730</v>
+        <v>7326964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128364523</v>
+        <v>128364546</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>78492</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607976</v>
+        <v>607943</v>
       </c>
       <c r="R18" t="n">
-        <v>7326679</v>
+        <v>7326659</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128364520</v>
+        <v>128364515</v>
       </c>
       <c r="B21" t="n">
         <v>79708</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608065</v>
+        <v>607656</v>
       </c>
       <c r="R21" t="n">
-        <v>7326779</v>
+        <v>7327054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128364515</v>
+        <v>128364520</v>
       </c>
       <c r="B22" t="n">
         <v>79708</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607656</v>
+        <v>608065</v>
       </c>
       <c r="R22" t="n">
-        <v>7327054</v>
+        <v>7326779</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128364540</v>
+        <v>128364535</v>
       </c>
       <c r="B31" t="n">
-        <v>78755</v>
+        <v>91485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607932</v>
+        <v>607955</v>
       </c>
       <c r="R31" t="n">
-        <v>7326666</v>
+        <v>7326918</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128364535</v>
+        <v>128364540</v>
       </c>
       <c r="B32" t="n">
-        <v>91485</v>
+        <v>78755</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607955</v>
+        <v>607932</v>
       </c>
       <c r="R32" t="n">
-        <v>7326918</v>
+        <v>7326666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128364539</v>
       </c>
       <c r="B3" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128364536</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128364521</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128364512</v>
       </c>
       <c r="B6" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128364542</v>
       </c>
       <c r="B7" t="n">
-        <v>78061</v>
+        <v>78088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>128364531</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364522</v>
+        <v>128364508</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>91416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608009</v>
+        <v>607664</v>
       </c>
       <c r="R9" t="n">
-        <v>7326713</v>
+        <v>7326860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,7 +1529,7 @@
         <v>128364526</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364508</v>
+        <v>128364522</v>
       </c>
       <c r="B11" t="n">
-        <v>91389</v>
+        <v>79735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607664</v>
+        <v>608009</v>
       </c>
       <c r="R11" t="n">
-        <v>7326860</v>
+        <v>7326713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,7 +1743,7 @@
         <v>128364533</v>
       </c>
       <c r="B12" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128364514</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>128364537</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128364513</v>
+        <v>128364546</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>78519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607761</v>
+        <v>607943</v>
       </c>
       <c r="R15" t="n">
-        <v>7326730</v>
+        <v>7326659</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128364523</v>
+        <v>128364513</v>
       </c>
       <c r="B16" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607976</v>
+        <v>607761</v>
       </c>
       <c r="R16" t="n">
-        <v>7326679</v>
+        <v>7326730</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,7 +2278,7 @@
         <v>128364527</v>
       </c>
       <c r="B17" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128364546</v>
+        <v>128364523</v>
       </c>
       <c r="B18" t="n">
-        <v>78492</v>
+        <v>79735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607943</v>
+        <v>607976</v>
       </c>
       <c r="R18" t="n">
-        <v>7326659</v>
+        <v>7326679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,7 +2492,7 @@
         <v>128364529</v>
       </c>
       <c r="B19" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>128364541</v>
       </c>
       <c r="B20" t="n">
-        <v>75169</v>
+        <v>75196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128364515</v>
+        <v>128364520</v>
       </c>
       <c r="B21" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607656</v>
+        <v>608065</v>
       </c>
       <c r="R21" t="n">
-        <v>7327054</v>
+        <v>7326779</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128364520</v>
+        <v>128364515</v>
       </c>
       <c r="B22" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>608065</v>
+        <v>607656</v>
       </c>
       <c r="R22" t="n">
-        <v>7326779</v>
+        <v>7327054</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,7 +2920,7 @@
         <v>128364517</v>
       </c>
       <c r="B23" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128364530</v>
+        <v>128364534</v>
       </c>
       <c r="B24" t="n">
-        <v>81074</v>
+        <v>91508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607658</v>
+        <v>607882</v>
       </c>
       <c r="R24" t="n">
-        <v>7326856</v>
+        <v>7326949</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128364534</v>
+        <v>128364530</v>
       </c>
       <c r="B25" t="n">
-        <v>91481</v>
+        <v>81101</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607882</v>
+        <v>607658</v>
       </c>
       <c r="R25" t="n">
-        <v>7326949</v>
+        <v>7326856</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,7 +3241,7 @@
         <v>128364545</v>
       </c>
       <c r="B26" t="n">
-        <v>78492</v>
+        <v>78519</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>128364516</v>
       </c>
       <c r="B27" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128364544</v>
+        <v>128364518</v>
       </c>
       <c r="B28" t="n">
-        <v>78492</v>
+        <v>79735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607746</v>
+        <v>608074</v>
       </c>
       <c r="R28" t="n">
-        <v>7326692</v>
+        <v>7326859</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128364509</v>
+        <v>128364544</v>
       </c>
       <c r="B29" t="n">
-        <v>75177</v>
+        <v>78519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607938</v>
+        <v>607746</v>
       </c>
       <c r="R29" t="n">
-        <v>7326914</v>
+        <v>7326692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128364518</v>
+        <v>128364509</v>
       </c>
       <c r="B30" t="n">
-        <v>79708</v>
+        <v>75204</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>608074</v>
+        <v>607938</v>
       </c>
       <c r="R30" t="n">
-        <v>7326859</v>
+        <v>7326914</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3776,7 +3776,7 @@
         <v>128364535</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128364540</v>
       </c>
       <c r="B32" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>128364538</v>
       </c>
       <c r="B33" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>128364528</v>
       </c>
       <c r="B34" t="n">
-        <v>80098</v>
+        <v>80125</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364536</v>
+        <v>128364521</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607676</v>
+        <v>608022</v>
       </c>
       <c r="R4" t="n">
-        <v>7326923</v>
+        <v>7326748</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364521</v>
+        <v>128364512</v>
       </c>
       <c r="B5" t="n">
         <v>79735</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608022</v>
+        <v>607775</v>
       </c>
       <c r="R5" t="n">
-        <v>7326748</v>
+        <v>7326678</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364512</v>
+        <v>128364536</v>
       </c>
       <c r="B6" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607775</v>
+        <v>607676</v>
       </c>
       <c r="R6" t="n">
-        <v>7326678</v>
+        <v>7326923</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128364542</v>
+        <v>128364531</v>
       </c>
       <c r="B7" t="n">
-        <v>78088</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608052</v>
+        <v>608103</v>
       </c>
       <c r="R7" t="n">
-        <v>7326905</v>
+        <v>7326855</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128364531</v>
+        <v>128364542</v>
       </c>
       <c r="B8" t="n">
-        <v>78873</v>
+        <v>78088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608103</v>
+        <v>608052</v>
       </c>
       <c r="R8" t="n">
-        <v>7326855</v>
+        <v>7326905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128364546</v>
+        <v>128364527</v>
       </c>
       <c r="B15" t="n">
-        <v>78519</v>
+        <v>80222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607943</v>
+        <v>607978</v>
       </c>
       <c r="R15" t="n">
-        <v>7326659</v>
+        <v>7326964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128364513</v>
+        <v>128364546</v>
       </c>
       <c r="B16" t="n">
-        <v>79735</v>
+        <v>78519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607761</v>
+        <v>607943</v>
       </c>
       <c r="R16" t="n">
-        <v>7326730</v>
+        <v>7326659</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128364527</v>
+        <v>128364513</v>
       </c>
       <c r="B17" t="n">
-        <v>80222</v>
+        <v>79735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607978</v>
+        <v>607761</v>
       </c>
       <c r="R17" t="n">
-        <v>7326964</v>
+        <v>7326730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128364535</v>
+        <v>128364540</v>
       </c>
       <c r="B31" t="n">
-        <v>91512</v>
+        <v>78782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607955</v>
+        <v>607932</v>
       </c>
       <c r="R31" t="n">
-        <v>7326918</v>
+        <v>7326666</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128364540</v>
+        <v>128364535</v>
       </c>
       <c r="B32" t="n">
-        <v>78782</v>
+        <v>91512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607932</v>
+        <v>607955</v>
       </c>
       <c r="R32" t="n">
-        <v>7326666</v>
+        <v>7326918</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4199,6 +4199,122 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129212437</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tjiärmadahkka , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>607846</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7326829</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -4204,7 +4204,7 @@
         <v>129212437</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -4204,7 +4204,7 @@
         <v>129212437</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -4204,7 +4204,7 @@
         <v>129212437</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -4204,7 +4204,7 @@
         <v>129212437</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127078104</v>
       </c>
       <c r="B2" t="n">
-        <v>57770</v>
+        <v>57761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127078104</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>57770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127078104</v>
+        <v>127078636</v>
       </c>
       <c r="B2" t="n">
-        <v>57770</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607755</v>
+        <v>607586</v>
       </c>
       <c r="R2" t="n">
-        <v>7326703</v>
+        <v>7326861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128364539</v>
+        <v>128364541</v>
       </c>
       <c r="B3" t="n">
-        <v>78790</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607806</v>
+        <v>607675</v>
       </c>
       <c r="R3" t="n">
-        <v>7327211</v>
+        <v>7326945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128364521</v>
+        <v>127078508</v>
       </c>
       <c r="B4" t="n">
-        <v>79743</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608022</v>
+        <v>607646</v>
       </c>
       <c r="R4" t="n">
-        <v>7326748</v>
+        <v>7326785</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:34</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:34</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128364512</v>
+        <v>128364538</v>
       </c>
       <c r="B5" t="n">
-        <v>79743</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607775</v>
+        <v>607660</v>
       </c>
       <c r="R5" t="n">
-        <v>7326678</v>
+        <v>7327032</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128364536</v>
+        <v>128364539</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607676</v>
+        <v>607806</v>
       </c>
       <c r="R6" t="n">
-        <v>7326923</v>
+        <v>7327211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128364542</v>
+        <v>128364540</v>
       </c>
       <c r="B7" t="n">
-        <v>78096</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608052</v>
+        <v>607932</v>
       </c>
       <c r="R7" t="n">
-        <v>7326905</v>
+        <v>7326666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128364531</v>
+        <v>128364530</v>
       </c>
       <c r="B8" t="n">
-        <v>78881</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608103</v>
+        <v>607658</v>
       </c>
       <c r="R8" t="n">
-        <v>7326855</v>
+        <v>7326856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1367,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1392,7 +1377,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128364508</v>
+        <v>128364533</v>
       </c>
       <c r="B9" t="n">
-        <v>91430</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607664</v>
+        <v>607928</v>
       </c>
       <c r="R9" t="n">
-        <v>7326860</v>
+        <v>7326925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1474,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1484,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,32 +1511,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128364522</v>
+        <v>128364534</v>
       </c>
       <c r="B10" t="n">
-        <v>79743</v>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608009</v>
+        <v>607882</v>
       </c>
       <c r="R10" t="n">
-        <v>7326713</v>
+        <v>7326949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1606,7 +1591,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,32 +1618,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364526</v>
+        <v>128364527</v>
       </c>
       <c r="B11" t="n">
-        <v>80258</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607883</v>
+        <v>607978</v>
       </c>
       <c r="R11" t="n">
-        <v>7326598</v>
+        <v>7326964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1688,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1713,7 +1698,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128364533</v>
+        <v>128364508</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607928</v>
+        <v>607664</v>
       </c>
       <c r="R12" t="n">
-        <v>7326925</v>
+        <v>7326860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1795,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1820,7 +1805,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128364514</v>
+        <v>127078644</v>
       </c>
       <c r="B13" t="n">
-        <v>79743</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,34 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607776</v>
+        <v>607586</v>
       </c>
       <c r="R13" t="n">
-        <v>7326788</v>
+        <v>7326861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,22 +1897,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:52</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:52</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,14 +1929,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128364537</v>
+        <v>128364536</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1989,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607897</v>
+        <v>607676</v>
       </c>
       <c r="R14" t="n">
-        <v>7326952</v>
+        <v>7326923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2034,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,32 +2036,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128364546</v>
+        <v>128364537</v>
       </c>
       <c r="B15" t="n">
-        <v>78527</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607943</v>
+        <v>607897</v>
       </c>
       <c r="R15" t="n">
-        <v>7326659</v>
+        <v>7326952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2106,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2141,7 +2116,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128364527</v>
+        <v>127074651</v>
       </c>
       <c r="B16" t="n">
-        <v>80230</v>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,34 +2154,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607978</v>
+        <v>607532</v>
       </c>
       <c r="R16" t="n">
-        <v>7326964</v>
+        <v>7326271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,22 +2208,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128364513</v>
+        <v>127078526</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,34 +2251,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607761</v>
+        <v>607630</v>
       </c>
       <c r="R17" t="n">
-        <v>7326730</v>
+        <v>7326801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,22 +2305,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:54</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:54</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128364529</v>
+        <v>128364544</v>
       </c>
       <c r="B18" t="n">
-        <v>80265</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607883</v>
+        <v>607746</v>
       </c>
       <c r="R18" t="n">
-        <v>7326598</v>
+        <v>7326692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2407,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2462,7 +2417,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128364523</v>
+        <v>128364545</v>
       </c>
       <c r="B19" t="n">
-        <v>79743</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607976</v>
+        <v>607771</v>
       </c>
       <c r="R19" t="n">
-        <v>7326679</v>
+        <v>7326790</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2514,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2524,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128364541</v>
+        <v>128364546</v>
       </c>
       <c r="B20" t="n">
-        <v>75201</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,16 +2562,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2631,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607675</v>
+        <v>607943</v>
       </c>
       <c r="R20" t="n">
-        <v>7326945</v>
+        <v>7326659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2621,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2676,7 +2631,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128364520</v>
+        <v>128364509</v>
       </c>
       <c r="B21" t="n">
-        <v>79743</v>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,21 +2669,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608065</v>
+        <v>607938</v>
       </c>
       <c r="R21" t="n">
-        <v>7326779</v>
+        <v>7326914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2728,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2783,7 +2738,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128364515</v>
+        <v>127074704</v>
       </c>
       <c r="B22" t="n">
-        <v>79743</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,34 +2776,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607656</v>
+        <v>607555</v>
       </c>
       <c r="R22" t="n">
-        <v>7327054</v>
+        <v>7326287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,22 +2830,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128364517</v>
+        <v>128364531</v>
       </c>
       <c r="B23" t="n">
-        <v>79743</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607902</v>
+        <v>608103</v>
       </c>
       <c r="R23" t="n">
-        <v>7327076</v>
+        <v>7326855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2932,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2997,7 +2942,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128364516</v>
+        <v>127079261</v>
       </c>
       <c r="B24" t="n">
-        <v>79743</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,14 +3000,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607722</v>
+        <v>607534</v>
       </c>
       <c r="R24" t="n">
-        <v>7327043</v>
+        <v>7326663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,22 +3034,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128364545</v>
+        <v>128364512</v>
       </c>
       <c r="B25" t="n">
-        <v>78527</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607771</v>
+        <v>607775</v>
       </c>
       <c r="R25" t="n">
-        <v>7326790</v>
+        <v>7326678</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3136,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3211,7 +3146,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128364530</v>
+        <v>128364513</v>
       </c>
       <c r="B26" t="n">
-        <v>81109</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,21 +3184,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3208,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607658</v>
+        <v>607761</v>
       </c>
       <c r="R26" t="n">
-        <v>7326856</v>
+        <v>7326730</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3243,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3318,7 +3253,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128364534</v>
+        <v>128364514</v>
       </c>
       <c r="B27" t="n">
-        <v>91522</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607882</v>
+        <v>607776</v>
       </c>
       <c r="R27" t="n">
-        <v>7326949</v>
+        <v>7326788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3350,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3425,7 +3360,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3452,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128364544</v>
+        <v>128364515</v>
       </c>
       <c r="B28" t="n">
-        <v>78527</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607746</v>
+        <v>607656</v>
       </c>
       <c r="R28" t="n">
-        <v>7326692</v>
+        <v>7327054</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3457,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3532,7 +3467,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128364509</v>
+        <v>128364516</v>
       </c>
       <c r="B29" t="n">
-        <v>75209</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,21 +3505,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607938</v>
+        <v>607722</v>
       </c>
       <c r="R29" t="n">
-        <v>7326914</v>
+        <v>7327043</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3564,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3574,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128364518</v>
+        <v>128364517</v>
       </c>
       <c r="B30" t="n">
-        <v>79743</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3701,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>608074</v>
+        <v>607902</v>
       </c>
       <c r="R30" t="n">
-        <v>7326859</v>
+        <v>7327076</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3671,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3746,7 +3681,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128364535</v>
+        <v>128364518</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3719,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3743,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607955</v>
+        <v>608074</v>
       </c>
       <c r="R31" t="n">
-        <v>7326918</v>
+        <v>7326859</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3778,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3788,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128364540</v>
+        <v>128364520</v>
       </c>
       <c r="B32" t="n">
-        <v>78790</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,21 +3826,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3850,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607932</v>
+        <v>608065</v>
       </c>
       <c r="R32" t="n">
-        <v>7326666</v>
+        <v>7326779</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,7 +3885,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +3895,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,10 +3922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128364538</v>
+        <v>128364521</v>
       </c>
       <c r="B33" t="n">
-        <v>78790</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3998,21 +3933,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +3957,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607660</v>
+        <v>608022</v>
       </c>
       <c r="R33" t="n">
-        <v>7327032</v>
+        <v>7326748</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +3992,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4067,7 +4002,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,32 +4029,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128364528</v>
+        <v>128364522</v>
       </c>
       <c r="B34" t="n">
-        <v>80133</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4129,10 +4064,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>607768</v>
+        <v>608009</v>
       </c>
       <c r="R34" t="n">
-        <v>7327150</v>
+        <v>7326713</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,7 +4099,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4174,7 +4109,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4201,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129212437</v>
+        <v>128364523</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4212,38 +4147,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka , Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>607846</v>
+        <v>607976</v>
       </c>
       <c r="R35" t="n">
-        <v>7326829</v>
+        <v>7326679</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4270,27 +4201,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4305,15 +4231,1679 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128364528</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>607768</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7327150</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128364526</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>607883</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7326598</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127074519</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>607517</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7326285</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128364529</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>607883</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7326598</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127076482</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>607764</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7326485</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128364542</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>608052</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7326905</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129211232</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tjiärmadahkka , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>607765</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7326469</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>Alva Danielsson</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Alva Danielsson</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129212437</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tjiärmadahkka , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>607846</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7326829</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127075079</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>607678</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7326420</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127078104</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>607755</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7326703</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127074251</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>607381</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7326163</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127079093</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>607489</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7326681</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127074716</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>607555</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7326287</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127078504</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>607646</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7326785</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128364524</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>607721</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7327042</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128364525</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Korsträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>608068</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7326863</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39728-2025 artfynd.xlsx
+++ b/artfynd/A 39728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127078636</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364541</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127078508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364538</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364539</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364540</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364530</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364533</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364534</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364527</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364508</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127078644</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364536</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364537</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074651</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2334,6 +2414,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127078526</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364544</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2548,6 +2638,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364545</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2655,6 +2750,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364546</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2762,6 +2862,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364509</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2859,6 +2964,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074704</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2966,6 +3076,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364531</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3063,6 +3178,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127079261</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3170,6 +3290,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364512</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3277,6 +3402,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364513</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3384,6 +3514,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364514</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3491,6 +3626,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364515</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3598,6 +3738,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364516</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3705,6 +3850,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364517</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3812,6 +3962,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364518</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3919,6 +4074,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364520</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4026,6 +4186,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364521</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4133,6 +4298,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364522</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4240,6 +4410,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364523</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4347,6 +4522,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4454,6 +4634,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364526</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4551,6 +4736,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074519</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4658,6 +4848,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364529</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4755,6 +4950,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076482</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4862,6 +5062,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364542</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4978,6 +5183,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129211232</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5094,6 +5304,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129212437</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5200,6 +5415,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127075079</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5302,6 +5522,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127078104</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5399,6 +5624,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074251</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5496,6 +5726,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127079093</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5593,6 +5828,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074716</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5690,6 +5930,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127078504</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5797,6 +6042,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364524</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5904,8 +6154,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128364525</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>